--- a/internal_doc/05.测试设计/驱动测试/PYTHON 驱动/python驱动测试设计及接口分析.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/PYTHON 驱动/python驱动测试设计及接口分析.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="4" r:id="rId1"/>
     <sheet name="测试设计" sheetId="5" r:id="rId2"/>
     <sheet name="接口分析" sheetId="1" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="新增域相关接口" sheetId="2" r:id="rId4"/>
+    <sheet name="新增复制组相关接口" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">接口分析!$E$1:$E$128</definedName>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="539">
   <si>
     <t>数据库操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2221,6 +2221,70 @@
   </si>
   <si>
     <t>网络异常、节点异常(通过异常类覆盖测试，放到后面)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.list_collection_spaces()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.list_collections()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_domain(domain_name)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_domain_existing(domain_name)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list_domains(kwargs)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_domain(domain_name)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_domain(domain_name,options = None)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.alter(options)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client.get_coord_replica_group()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client.get_cata_replica_group()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client.create_coord_replica_group()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client.remove_coord_replica_group()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client.remove_cata_replica_group()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client.start_replica_group(group_name)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">client.stop_replica_group(group_name) </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2321,16 +2385,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2359,6 +2420,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2687,7 +2757,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" ht="81">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>505</v>
       </c>
     </row>
@@ -2717,7 +2787,7 @@
       </c>
     </row>
     <row r="12" spans="1:1" ht="27">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>512</v>
       </c>
     </row>
@@ -2783,14 +2853,14 @@
       <c r="B2" t="s">
         <v>376</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="16" t="s">
+      <c r="D2" s="16"/>
+      <c r="E2" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>514</v>
       </c>
     </row>
@@ -2848,7 +2918,7 @@
       <c r="D7" t="s">
         <v>388</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="19" t="s">
         <v>449</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2859,7 +2929,7 @@
       <c r="D8" t="s">
         <v>389</v>
       </c>
-      <c r="E8" s="3"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="1" t="s">
         <v>448</v>
       </c>
@@ -2871,7 +2941,7 @@
       <c r="D9" t="s">
         <v>328</v>
       </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="1" t="s">
         <v>328</v>
       </c>
@@ -2880,7 +2950,7 @@
       <c r="D10" t="s">
         <v>325</v>
       </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="19"/>
       <c r="F10" s="1" t="s">
         <v>325</v>
       </c>
@@ -2892,7 +2962,7 @@
       <c r="D11" t="s">
         <v>264</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="1" t="s">
         <v>264</v>
       </c>
@@ -2901,7 +2971,7 @@
       <c r="D12" t="s">
         <v>392</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="19"/>
       <c r="F12" s="1" t="s">
         <v>392</v>
       </c>
@@ -2913,7 +2983,7 @@
       <c r="D13" t="s">
         <v>394</v>
       </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="1" t="s">
         <v>454</v>
       </c>
@@ -2922,7 +2992,7 @@
       <c r="D14" t="s">
         <v>373</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="1" t="s">
         <v>456</v>
       </c>
@@ -3066,78 +3136,78 @@
       </c>
     </row>
     <row r="30" spans="2:6" ht="27">
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14" t="s">
+      <c r="C30" s="13"/>
+      <c r="D30" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="14" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="27">
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15" t="s">
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="14" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15" t="s">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="27">
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="15" t="s">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="14" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="27">
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="15" t="s">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="14" t="s">
         <v>496</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="14" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15" t="s">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14" t="s">
         <v>153</v>
       </c>
     </row>
@@ -3184,80 +3254,80 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="27">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="14" t="s">
         <v>508</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="15" t="s">
+      <c r="D39" s="13"/>
+      <c r="E39" s="14" t="s">
         <v>490</v>
       </c>
-      <c r="F39" s="15"/>
+      <c r="F39" s="14"/>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="15"/>
-      <c r="B40" s="14" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="15" t="s">
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="14" t="s">
         <v>516</v>
       </c>
-      <c r="F40" s="15"/>
+      <c r="F40" s="14"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="15"/>
-      <c r="B41" s="14" t="s">
+      <c r="A41" s="14"/>
+      <c r="B41" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="15" t="s">
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="14" t="s">
         <v>516</v>
       </c>
-      <c r="F41" s="15"/>
+      <c r="F41" s="14"/>
     </row>
     <row r="42" spans="1:6" ht="27">
-      <c r="A42" s="15"/>
-      <c r="B42" s="14" t="s">
+      <c r="A42" s="14"/>
+      <c r="B42" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="15" t="s">
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="14" t="s">
         <v>522</v>
       </c>
-      <c r="F42" s="15"/>
+      <c r="F42" s="14"/>
     </row>
     <row r="43" spans="1:6" ht="27">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16" t="s">
+      <c r="B43" s="16"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="27">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="F44" s="6"/>
+      <c r="F44" s="5"/>
     </row>
     <row r="45" spans="1:6" ht="27">
       <c r="A45" s="1" t="s">
@@ -3268,16 +3338,16 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="27">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="14" t="s">
         <v>501</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="15" t="s">
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="F46" s="15"/>
+      <c r="F46" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3290,6 +3360,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3329,7 +3400,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" hidden="1">
       <c r="A2" t="s">
         <v>337</v>
       </c>
@@ -3342,7 +3413,7 @@
       <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>98</v>
       </c>
       <c r="F2" t="s">
@@ -3352,14 +3423,14 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27">
+    <row r="3" spans="1:8" ht="27" hidden="1">
       <c r="C3" t="s">
         <v>105</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>431</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -3369,14 +3440,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="C4" t="s">
         <v>107</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>106</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -3386,14 +3457,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27">
+    <row r="5" spans="1:8" ht="27" hidden="1">
       <c r="C5" t="s">
         <v>109</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>108</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -3403,14 +3474,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27">
+    <row r="6" spans="1:8" ht="27" hidden="1">
       <c r="C6" t="s">
         <v>112</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>111</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -3420,14 +3491,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27">
+    <row r="7" spans="1:8" ht="27" hidden="1">
       <c r="C7" t="s">
         <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -3437,14 +3508,14 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="C8" t="s">
         <v>119</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>118</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -3454,14 +3525,14 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27">
+    <row r="9" spans="1:8" ht="27" hidden="1">
       <c r="C9" t="s">
         <v>130</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>122</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -3471,14 +3542,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="C10" t="s">
         <v>128</v>
       </c>
       <c r="D10" t="s">
         <v>127</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>125</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -3488,14 +3559,14 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="C11" t="s">
         <v>133</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>132</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -3505,14 +3576,14 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="C12" t="s">
         <v>137</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>136</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -3522,14 +3593,14 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" hidden="1">
       <c r="C13" t="s">
         <v>139</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>140</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -3539,14 +3610,14 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="C14" t="s">
         <v>143</v>
       </c>
       <c r="D14" t="s">
         <v>144</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>142</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -3556,14 +3627,14 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" hidden="1">
       <c r="C15" t="s">
         <v>150</v>
       </c>
       <c r="D15" t="s">
         <v>144</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>426</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -3573,14 +3644,14 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="C16" t="s">
         <v>151</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>149</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -3590,14 +3661,14 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="3:8">
+    <row r="17" spans="3:8" hidden="1">
       <c r="C17" t="s">
         <v>156</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>153</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -3607,28 +3678,28 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="3:8">
+    <row r="18" spans="3:8" hidden="1">
       <c r="C18" t="s">
         <v>158</v>
       </c>
       <c r="D18" t="s">
         <v>85</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="3:8">
+    <row r="19" spans="3:8" hidden="1">
       <c r="C19" t="s">
         <v>159</v>
       </c>
       <c r="D19" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>160</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -3638,22 +3709,22 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="3:8">
-      <c r="E20" s="5" t="s">
+    <row r="20" spans="3:8" hidden="1">
+      <c r="E20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="3:8" ht="27">
+    <row r="21" spans="3:8" ht="27" hidden="1">
       <c r="C21" t="s">
         <v>164</v>
       </c>
       <c r="D21" t="s">
         <v>144</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>163</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -3663,14 +3734,14 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="3:8">
+    <row r="22" spans="3:8" hidden="1">
       <c r="C22" t="s">
         <v>168</v>
       </c>
       <c r="D22" t="s">
         <v>127</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="11" t="s">
         <v>167</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -3680,14 +3751,14 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="3:8">
+    <row r="23" spans="3:8" hidden="1">
       <c r="C23" t="s">
         <v>168</v>
       </c>
       <c r="D23" t="s">
         <v>127</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="11" t="s">
         <v>171</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -3697,14 +3768,14 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="3:8" ht="27">
+    <row r="24" spans="3:8" ht="27" hidden="1">
       <c r="C24" t="s">
         <v>172</v>
       </c>
       <c r="D24" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="11" t="s">
         <v>432</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -3714,14 +3785,14 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="3:8">
+    <row r="25" spans="3:8" hidden="1">
       <c r="C25" t="s">
         <v>176</v>
       </c>
       <c r="D25" t="s">
         <v>175</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="11" t="s">
         <v>174</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -3731,14 +3802,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="3:8">
+    <row r="26" spans="3:8" hidden="1">
       <c r="C26" t="s">
         <v>179</v>
       </c>
       <c r="D26" t="s">
         <v>144</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="11" t="s">
         <v>177</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -3748,14 +3819,14 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="3:8">
+    <row r="27" spans="3:8" hidden="1">
       <c r="C27" t="s">
         <v>181</v>
       </c>
       <c r="D27" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="11" t="s">
         <v>440</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -3765,14 +3836,14 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="3:8">
+    <row r="28" spans="3:8" hidden="1">
       <c r="C28" t="s">
         <v>183</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="11" t="s">
         <v>446</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -3782,14 +3853,14 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="3:8">
+    <row r="29" spans="3:8" hidden="1">
       <c r="C29" t="s">
         <v>188</v>
       </c>
       <c r="D29" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="11" t="s">
         <v>182</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -3799,14 +3870,14 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="3:8">
+    <row r="30" spans="3:8" hidden="1">
       <c r="C30" t="s">
         <v>190</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="11" t="s">
         <v>189</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -3816,14 +3887,14 @@
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="3:8">
+    <row r="31" spans="3:8" hidden="1">
       <c r="C31" t="s">
         <v>193</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="11" t="s">
         <v>192</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -3833,14 +3904,14 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="3:8">
+    <row r="32" spans="3:8" hidden="1">
       <c r="C32" t="s">
         <v>196</v>
       </c>
       <c r="D32" t="s">
         <v>197</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="11" t="s">
         <v>198</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -3850,14 +3921,14 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="3:8">
+    <row r="33" spans="3:8" hidden="1">
       <c r="C33" t="s">
         <v>202</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="11" t="s">
         <v>201</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -3867,14 +3938,14 @@
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="3:8">
+    <row r="34" spans="3:8" hidden="1">
       <c r="C34" t="s">
         <v>204</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="11" t="s">
         <v>205</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -3884,14 +3955,14 @@
         <v>206</v>
       </c>
     </row>
-    <row r="35" spans="3:8">
+    <row r="35" spans="3:8" hidden="1">
       <c r="C35" t="s">
         <v>208</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="11" t="s">
         <v>207</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -3901,14 +3972,14 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="3:8">
+    <row r="36" spans="3:8" hidden="1">
       <c r="C36" t="s">
         <v>211</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="11" t="s">
         <v>433</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -3918,31 +3989,31 @@
         <v>212</v>
       </c>
     </row>
-    <row r="37" spans="3:8" ht="27">
+    <row r="37" spans="3:8" ht="27" hidden="1">
       <c r="C37" t="s">
         <v>214</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>215</v>
       </c>
       <c r="H37" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="38" spans="3:8">
+    <row r="38" spans="3:8" hidden="1">
       <c r="C38" t="s">
         <v>217</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="11" t="s">
         <v>436</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -3952,14 +4023,14 @@
         <v>218</v>
       </c>
     </row>
-    <row r="39" spans="3:8">
+    <row r="39" spans="3:8" hidden="1">
       <c r="C39" t="s">
         <v>222</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="11" t="s">
         <v>219</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -3969,14 +4040,14 @@
         <v>225</v>
       </c>
     </row>
-    <row r="40" spans="3:8">
+    <row r="40" spans="3:8" hidden="1">
       <c r="C40" t="s">
         <v>223</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="11" t="s">
         <v>220</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -3986,14 +4057,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="41" spans="3:8">
+    <row r="41" spans="3:8" hidden="1">
       <c r="C41" t="s">
         <v>224</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="11" t="s">
         <v>221</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -4003,17 +4074,17 @@
         <v>227</v>
       </c>
     </row>
-    <row r="42" spans="3:8" ht="27">
+    <row r="42" spans="3:8" ht="27" hidden="1">
       <c r="C42" t="s">
         <v>229</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="7" t="s">
         <v>230</v>
       </c>
       <c r="H42" t="s">
@@ -4026,7 +4097,7 @@
         <v>48</v>
       </c>
       <c r="F43" s="1"/>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="4" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4036,7 +4107,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="1"/>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="4" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4054,7 +4125,7 @@
         <v>48</v>
       </c>
       <c r="F46" s="1"/>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="4" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4112,7 +4183,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
+    <row r="53" spans="2:8" hidden="1">
       <c r="B53" t="s">
         <v>242</v>
       </c>
@@ -4122,29 +4193,29 @@
       <c r="D53" t="s">
         <v>82</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
+    <row r="54" spans="2:8" hidden="1">
       <c r="C54" t="s">
         <v>81</v>
       </c>
       <c r="D54" t="s">
         <v>82</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="27">
+    <row r="55" spans="2:8" ht="27" hidden="1">
       <c r="C55" t="s">
         <v>84</v>
       </c>
       <c r="D55" t="s">
         <v>85</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="11" t="s">
         <v>78</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -4154,14 +4225,14 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
+    <row r="56" spans="2:8" hidden="1">
       <c r="C56" t="s">
         <v>88</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="11" t="s">
         <v>87</v>
       </c>
       <c r="F56" t="s">
@@ -4171,14 +4242,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
+    <row r="57" spans="2:8" hidden="1">
       <c r="C57" t="s">
         <v>91</v>
       </c>
       <c r="D57" t="s">
         <v>85</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="11" t="s">
         <v>90</v>
       </c>
       <c r="F57" t="s">
@@ -4188,14 +4259,14 @@
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
+    <row r="58" spans="2:8" hidden="1">
       <c r="C58" t="s">
         <v>95</v>
       </c>
       <c r="D58" t="s">
         <v>96</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="11" t="s">
         <v>94</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -4205,7 +4276,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
+    <row r="59" spans="2:8" hidden="1">
       <c r="B59" t="s">
         <v>243</v>
       </c>
@@ -4215,7 +4286,7 @@
       <c r="D59" t="s">
         <v>144</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="11" t="s">
         <v>244</v>
       </c>
       <c r="F59" t="s">
@@ -4225,14 +4296,14 @@
         <v>246</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
+    <row r="60" spans="2:8" hidden="1">
       <c r="C60" t="s">
         <v>249</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="11" t="s">
         <v>452</v>
       </c>
       <c r="F60" t="s">
@@ -4242,14 +4313,14 @@
         <v>250</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
+    <row r="61" spans="2:8" hidden="1">
       <c r="C61" t="s">
         <v>252</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="11" t="s">
         <v>448</v>
       </c>
       <c r="F61" t="s">
@@ -4259,14 +4330,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="2:8" ht="40.5">
+    <row r="62" spans="2:8" ht="40.5" hidden="1">
       <c r="C62" t="s">
         <v>255</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="11" t="s">
         <v>254</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -4276,14 +4347,14 @@
         <v>257</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
+    <row r="63" spans="2:8" hidden="1">
       <c r="C63" t="s">
         <v>259</v>
       </c>
       <c r="D63" t="s">
         <v>262</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="11" t="s">
         <v>258</v>
       </c>
       <c r="F63" t="s">
@@ -4293,14 +4364,14 @@
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
+    <row r="64" spans="2:8" hidden="1">
       <c r="C64" t="s">
         <v>265</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="11" t="s">
         <v>264</v>
       </c>
       <c r="F64" t="s">
@@ -4310,14 +4381,14 @@
         <v>266</v>
       </c>
     </row>
-    <row r="65" spans="3:8">
+    <row r="65" spans="3:8" hidden="1">
       <c r="C65" t="s">
         <v>268</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="11" t="s">
         <v>267</v>
       </c>
       <c r="F65" t="s">
@@ -4327,14 +4398,14 @@
         <v>270</v>
       </c>
     </row>
-    <row r="66" spans="3:8">
+    <row r="66" spans="3:8" hidden="1">
       <c r="C66" t="s">
         <v>271</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="11" t="s">
         <v>457</v>
       </c>
       <c r="F66" t="s">
@@ -4344,14 +4415,14 @@
         <v>273</v>
       </c>
     </row>
-    <row r="67" spans="3:8">
+    <row r="67" spans="3:8" hidden="1">
       <c r="C67" t="s">
         <v>276</v>
       </c>
       <c r="D67" t="s">
         <v>144</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="11" t="s">
         <v>274</v>
       </c>
       <c r="F67" t="s">
@@ -4361,14 +4432,14 @@
         <v>277</v>
       </c>
     </row>
-    <row r="68" spans="3:8">
+    <row r="68" spans="3:8" hidden="1">
       <c r="C68" t="s">
         <v>280</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="11" t="s">
         <v>278</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -4378,14 +4449,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="3:8">
+    <row r="69" spans="3:8" hidden="1">
       <c r="C69" t="s">
         <v>282</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="11" t="s">
         <v>281</v>
       </c>
       <c r="F69" t="s">
@@ -4395,14 +4466,14 @@
         <v>284</v>
       </c>
     </row>
-    <row r="70" spans="3:8">
+    <row r="70" spans="3:8" hidden="1">
       <c r="C70" t="s">
         <v>95</v>
       </c>
       <c r="D70" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="11" t="s">
         <v>285</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -4412,14 +4483,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="3:8">
+    <row r="71" spans="3:8" hidden="1">
       <c r="C71" t="s">
         <v>287</v>
       </c>
       <c r="D71" t="s">
         <v>288</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="11" t="s">
         <v>286</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -4429,14 +4500,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="3:8">
+    <row r="72" spans="3:8" hidden="1">
       <c r="C72" t="s">
         <v>291</v>
       </c>
       <c r="D72" t="s">
         <v>197</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="11" t="s">
         <v>289</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -4446,14 +4517,14 @@
         <v>330</v>
       </c>
     </row>
-    <row r="73" spans="3:8">
+    <row r="73" spans="3:8" hidden="1">
       <c r="C73" t="s">
         <v>292</v>
       </c>
       <c r="D73" t="s">
         <v>262</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="11" t="s">
         <v>468</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -4463,32 +4534,32 @@
         <v>294</v>
       </c>
     </row>
-    <row r="74" spans="3:8">
-      <c r="C74" s="5" t="s">
+    <row r="74" spans="3:8" hidden="1">
+      <c r="C74" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5" t="s">
+      <c r="G74" s="4"/>
+      <c r="H74" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="3:8">
+    <row r="75" spans="3:8" hidden="1">
       <c r="C75" t="s">
         <v>299</v>
       </c>
       <c r="D75" t="s">
         <v>298</v>
       </c>
-      <c r="E75" s="12" t="s">
+      <c r="E75" s="11" t="s">
         <v>388</v>
       </c>
       <c r="F75" s="1" t="s">
@@ -4498,14 +4569,14 @@
         <v>297</v>
       </c>
     </row>
-    <row r="76" spans="3:8">
+    <row r="76" spans="3:8" hidden="1">
       <c r="C76" t="s">
         <v>302</v>
       </c>
       <c r="D76" t="s">
         <v>197</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="E76" s="11" t="s">
         <v>300</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -4515,14 +4586,14 @@
         <v>301</v>
       </c>
     </row>
-    <row r="77" spans="3:8">
+    <row r="77" spans="3:8" hidden="1">
       <c r="C77" t="s">
         <v>304</v>
       </c>
       <c r="D77" t="s">
         <v>197</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="E77" s="11" t="s">
         <v>394</v>
       </c>
       <c r="F77" s="1" t="s">
@@ -4532,14 +4603,14 @@
         <v>303</v>
       </c>
     </row>
-    <row r="78" spans="3:8">
+    <row r="78" spans="3:8" hidden="1">
       <c r="C78" t="s">
         <v>305</v>
       </c>
       <c r="D78" t="s">
         <v>197</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="11" t="s">
         <v>450</v>
       </c>
       <c r="F78" s="1" t="s">
@@ -4549,14 +4620,14 @@
         <v>306</v>
       </c>
     </row>
-    <row r="79" spans="3:8">
+    <row r="79" spans="3:8" hidden="1">
       <c r="C79" t="s">
         <v>307</v>
       </c>
       <c r="D79" t="s">
         <v>197</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="11" t="s">
         <v>451</v>
       </c>
       <c r="F79" s="1" t="s">
@@ -4566,14 +4637,14 @@
         <v>308</v>
       </c>
     </row>
-    <row r="80" spans="3:8">
+    <row r="80" spans="3:8" hidden="1">
       <c r="C80" t="s">
         <v>311</v>
       </c>
       <c r="D80" t="s">
         <v>310</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="E80" s="11" t="s">
         <v>309</v>
       </c>
       <c r="F80" s="1" t="s">
@@ -4583,14 +4654,14 @@
         <v>329</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" hidden="1">
       <c r="C81" t="s">
         <v>312</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="E81" s="11" t="s">
         <v>469</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -4600,26 +4671,26 @@
         <v>336</v>
       </c>
     </row>
-    <row r="82" spans="2:8">
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5" t="s">
+    <row r="82" spans="2:8" hidden="1">
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F82" s="6"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5" t="s">
+      <c r="F82" s="5"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="54">
+    <row r="83" spans="2:8" ht="54" hidden="1">
       <c r="C83" t="s">
         <v>316</v>
       </c>
       <c r="D83" t="s">
         <v>322</v>
       </c>
-      <c r="E83" s="12" t="s">
+      <c r="E83" s="11" t="s">
         <v>315</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -4629,14 +4700,14 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="27">
+    <row r="84" spans="2:8" ht="27" hidden="1">
       <c r="C84" t="s">
         <v>318</v>
       </c>
       <c r="D84" t="s">
         <v>322</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="11" t="s">
         <v>317</v>
       </c>
       <c r="F84" s="1" t="s">
@@ -4646,14 +4717,14 @@
         <v>332</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="54">
+    <row r="85" spans="2:8" ht="54" hidden="1">
       <c r="C85" t="s">
         <v>319</v>
       </c>
       <c r="D85" t="s">
         <v>322</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="11" t="s">
         <v>472</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -4663,14 +4734,14 @@
         <v>331</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="27">
+    <row r="86" spans="2:8" ht="27" hidden="1">
       <c r="C86" t="s">
         <v>320</v>
       </c>
       <c r="D86" t="s">
         <v>322</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="11" t="s">
         <v>321</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -4680,14 +4751,14 @@
         <v>331</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="27">
+    <row r="87" spans="2:8" ht="27" hidden="1">
       <c r="C87" t="s">
         <v>327</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E87" s="12" t="s">
+      <c r="E87" s="11" t="s">
         <v>325</v>
       </c>
       <c r="F87" s="1" t="s">
@@ -4697,14 +4768,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="27">
+    <row r="88" spans="2:8" ht="27" hidden="1">
       <c r="C88" t="s">
         <v>327</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E88" s="13" t="s">
+      <c r="E88" s="12" t="s">
         <v>328</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -4722,49 +4793,49 @@
         <v>251</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" hidden="1">
       <c r="C90" t="s">
         <v>464</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E90" s="12" t="s">
+      <c r="E90" s="11" t="s">
         <v>462</v>
       </c>
       <c r="H90" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" hidden="1">
       <c r="C91" t="s">
         <v>465</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="E91" s="11" t="s">
         <v>461</v>
       </c>
       <c r="H91" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" hidden="1">
       <c r="C92" t="s">
         <v>466</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E92" s="12" t="s">
+      <c r="E92" s="11" t="s">
         <v>392</v>
       </c>
       <c r="H92" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="40.5">
+    <row r="93" spans="2:8" ht="40.5" hidden="1">
       <c r="B93" t="s">
         <v>374</v>
       </c>
@@ -4774,231 +4845,231 @@
       <c r="D93" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E93" s="12" t="s">
+      <c r="E93" s="11" t="s">
         <v>479</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="20" t="s">
         <v>52</v>
       </c>
       <c r="H93" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="40.5">
+    <row r="94" spans="2:8" ht="40.5" hidden="1">
       <c r="C94" t="s">
         <v>10</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="E94" s="11" t="s">
         <v>480</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G94" s="4"/>
+      <c r="G94" s="20"/>
       <c r="H94" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="27">
+    <row r="95" spans="2:8" ht="27" hidden="1">
       <c r="C95" t="s">
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E95" s="12" t="s">
+      <c r="E95" s="11" t="s">
         <v>481</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G95" s="4"/>
+      <c r="G95" s="20"/>
       <c r="H95" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" hidden="1">
       <c r="C96" t="s">
         <v>12</v>
       </c>
       <c r="D96" t="s">
         <v>17</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="E96" s="11" t="s">
         <v>474</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G96" s="4"/>
+      <c r="G96" s="20"/>
       <c r="H96" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" hidden="1">
       <c r="C97" t="s">
         <v>13</v>
       </c>
       <c r="D97" t="s">
         <v>16</v>
       </c>
-      <c r="E97" s="12" t="s">
+      <c r="E97" s="11" t="s">
         <v>482</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G97" s="4"/>
+      <c r="G97" s="20"/>
       <c r="H97" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" hidden="1">
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
         <v>16</v>
       </c>
-      <c r="E98" s="12" t="s">
+      <c r="E98" s="11" t="s">
         <v>483</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G98" s="4"/>
+      <c r="G98" s="20"/>
       <c r="H98" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="99" spans="2:8">
+    <row r="99" spans="2:8" hidden="1">
       <c r="C99" t="s">
         <v>14</v>
       </c>
       <c r="D99" t="s">
         <v>16</v>
       </c>
-      <c r="E99" s="12" t="s">
+      <c r="E99" s="11" t="s">
         <v>484</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G99" s="4"/>
+      <c r="G99" s="20"/>
       <c r="H99" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" hidden="1">
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
         <v>32</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="E100" s="11" t="s">
         <v>485</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G100" s="4"/>
+      <c r="G100" s="20"/>
       <c r="H100" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="101" spans="2:8">
+    <row r="101" spans="2:8" hidden="1">
       <c r="C101" t="s">
         <v>19</v>
       </c>
       <c r="D101" t="s">
         <v>16</v>
       </c>
-      <c r="E101" s="12" t="s">
+      <c r="E101" s="11" t="s">
         <v>486</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G101" s="4"/>
+      <c r="G101" s="20"/>
       <c r="H101" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" hidden="1">
       <c r="C102" t="s">
         <v>21</v>
       </c>
       <c r="D102" t="s">
         <v>22</v>
       </c>
-      <c r="E102" s="12" t="s">
+      <c r="E102" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G102" s="4"/>
+      <c r="G102" s="20"/>
       <c r="H102" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="27">
+    <row r="103" spans="2:8" ht="27" hidden="1">
       <c r="C103" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E103" s="12" t="s">
+      <c r="E103" s="11" t="s">
         <v>487</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G103" s="4"/>
+      <c r="G103" s="20"/>
       <c r="H103" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" hidden="1">
       <c r="C104" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E104" s="12" t="s">
+      <c r="E104" s="11" t="s">
         <v>67</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G104" s="4"/>
+      <c r="G104" s="20"/>
       <c r="H104" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="105" spans="2:8">
+    <row r="105" spans="2:8" hidden="1">
       <c r="C105" t="s">
         <v>25</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="E105" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G105" s="4"/>
+      <c r="G105" s="20"/>
       <c r="H105" t="s">
         <v>46</v>
       </c>
@@ -5007,12 +5078,12 @@
       <c r="E106" t="s">
         <v>48</v>
       </c>
-      <c r="G106" s="4"/>
+      <c r="G106" s="20"/>
       <c r="H106" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="107" spans="2:8">
+    <row r="107" spans="2:8" hidden="1">
       <c r="B107" t="s">
         <v>375</v>
       </c>
@@ -5022,7 +5093,7 @@
       <c r="D107" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E107" s="12" t="s">
+      <c r="E107" s="11" t="s">
         <v>53</v>
       </c>
       <c r="F107" s="1" t="s">
@@ -5032,14 +5103,14 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="2:8">
+    <row r="108" spans="2:8" hidden="1">
       <c r="C108" t="s">
         <v>57</v>
       </c>
       <c r="D108" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="12" t="s">
+      <c r="E108" s="11" t="s">
         <v>55</v>
       </c>
       <c r="F108" s="1" t="s">
@@ -5049,14 +5120,14 @@
         <v>71</v>
       </c>
     </row>
-    <row r="109" spans="2:8">
+    <row r="109" spans="2:8" hidden="1">
       <c r="C109" t="s">
         <v>60</v>
       </c>
       <c r="D109" t="s">
         <v>59</v>
       </c>
-      <c r="E109" s="12" t="s">
+      <c r="E109" s="11" t="s">
         <v>58</v>
       </c>
       <c r="F109" s="1" t="s">
@@ -5066,14 +5137,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="110" spans="2:8">
+    <row r="110" spans="2:8" hidden="1">
       <c r="C110" t="s">
         <v>63</v>
       </c>
       <c r="D110" t="s">
         <v>62</v>
       </c>
-      <c r="E110" s="12" t="s">
+      <c r="E110" s="11" t="s">
         <v>61</v>
       </c>
       <c r="F110" s="1" t="s">
@@ -5083,14 +5154,14 @@
         <v>73</v>
       </c>
     </row>
-    <row r="111" spans="2:8">
+    <row r="111" spans="2:8" hidden="1">
       <c r="C111" t="s">
         <v>66</v>
       </c>
       <c r="D111" t="s">
         <v>65</v>
       </c>
-      <c r="E111" s="12" t="s">
+      <c r="E111" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F111" s="1" t="s">
@@ -5100,14 +5171,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="112" spans="2:8">
+    <row r="112" spans="2:8" hidden="1">
       <c r="C112" t="s">
         <v>68</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E112" s="12" t="s">
+      <c r="E112" s="11" t="s">
         <v>67</v>
       </c>
       <c r="F112" s="1" t="s">
@@ -5117,14 +5188,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" hidden="1">
       <c r="C113" t="s">
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E113" s="12" t="s">
+      <c r="E113" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F113" s="1" t="s">
@@ -5134,7 +5205,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" hidden="1">
       <c r="B114" t="s">
         <v>373</v>
       </c>
@@ -5144,7 +5215,7 @@
       <c r="D114" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E114" s="12" t="s">
+      <c r="E114" s="11" t="s">
         <v>340</v>
       </c>
       <c r="F114" s="1" t="s">
@@ -5154,14 +5225,14 @@
         <v>138</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" hidden="1">
       <c r="C115" t="s">
         <v>346</v>
       </c>
       <c r="D115" t="s">
         <v>344</v>
       </c>
-      <c r="E115" s="12" t="s">
+      <c r="E115" s="11" t="s">
         <v>341</v>
       </c>
       <c r="F115" s="1" t="s">
@@ -5171,14 +5242,14 @@
         <v>348</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" hidden="1">
       <c r="C116" t="s">
         <v>347</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E116" s="12" t="s">
+      <c r="E116" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F116" s="1" t="s">
@@ -5189,32 +5260,32 @@
       </c>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10" t="s">
+      <c r="A117" s="9"/>
+      <c r="B117" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C117" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="D117" s="10"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="10"/>
-      <c r="G117" s="10"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="9"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="11"/>
-      <c r="B118" s="11" t="s">
+      <c r="A118" s="10"/>
+      <c r="B118" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="11"/>
-    </row>
-    <row r="119" spans="1:8">
+      <c r="D118" s="10"/>
+      <c r="E118" s="10"/>
+      <c r="F118" s="10"/>
+      <c r="G118" s="10"/>
+    </row>
+    <row r="119" spans="1:8" hidden="1">
       <c r="B119" t="s">
         <v>261</v>
       </c>
@@ -5224,91 +5295,91 @@
       <c r="D119" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E119" s="12" t="s">
+      <c r="E119" s="11" t="s">
         <v>340</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" hidden="1">
       <c r="C120" t="s">
         <v>355</v>
       </c>
       <c r="D120" t="s">
         <v>356</v>
       </c>
-      <c r="E120" s="12" t="s">
+      <c r="E120" s="11" t="s">
         <v>354</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" hidden="1">
       <c r="C121" t="s">
         <v>358</v>
       </c>
       <c r="D121" t="s">
         <v>298</v>
       </c>
-      <c r="E121" s="12" t="s">
+      <c r="E121" s="11" t="s">
         <v>357</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" hidden="1">
       <c r="C122" t="s">
         <v>360</v>
       </c>
       <c r="D122" t="s">
         <v>361</v>
       </c>
-      <c r="E122" s="12" t="s">
+      <c r="E122" s="11" t="s">
         <v>359</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" hidden="1">
       <c r="C123" t="s">
         <v>363</v>
       </c>
       <c r="D123" t="s">
         <v>364</v>
       </c>
-      <c r="E123" s="12" t="s">
+      <c r="E123" s="11" t="s">
         <v>362</v>
       </c>
       <c r="F123" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="27">
+    <row r="124" spans="1:8" ht="27" hidden="1">
       <c r="C124" t="s">
         <v>368</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E124" s="12" t="s">
+      <c r="E124" s="11" t="s">
         <v>366</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" hidden="1">
       <c r="C125" t="s">
         <v>371</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E125" s="12" t="s">
+      <c r="E125" s="11" t="s">
         <v>369</v>
       </c>
       <c r="F125" s="1" t="s">
@@ -5324,7 +5395,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E128"/>
+  <autoFilter ref="E1:E128">
+    <filterColumn colId="0">
+      <filters blank="1">
+        <filter val="无"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="G93:G106"/>
   </mergeCells>
@@ -5336,9 +5413,83 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="43.625" customWidth="1"/>
+    <col min="4" max="4" width="19.75" customWidth="1"/>
+    <col min="5" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="6" width="40.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="C2" s="13" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="C3" s="13" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="C4" s="13" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="C5" s="13" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="C6" s="13" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="C7" s="13" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="C8" s="13" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="C9" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="C10" t="s">
+        <v>525</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5346,9 +5497,71 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="28.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27">
+      <c r="C2" s="18" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27">
+      <c r="C3" s="18" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="C4" s="18" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="27">
+      <c r="C5" s="18" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27">
+      <c r="C6" s="18" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27">
+      <c r="C7" s="18" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="27">
+      <c r="C8" s="18" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
